--- a/etl/data/mis/1200351 - marechal thaumaturgo.xlsx
+++ b/etl/data/mis/1200351 - marechal thaumaturgo.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Ano Mês (AAAAMM)</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>codigo</t>
+  </si>
+  <si>
+    <t>BPC por município pagador - Quantidade bpc beneficiário total</t>
   </si>
 </sst>
 </file>
@@ -443,6 +446,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K157"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="8" max="10" width="11.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -458,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -492,8 +500,8 @@
       <c r="D2" s="1">
         <v>620364</v>
       </c>
-      <c r="E2" s="1">
-        <v>620364</v>
+      <c r="E2">
+        <v>24</v>
       </c>
       <c r="F2">
         <v>13</v>
@@ -527,8 +535,8 @@
       <c r="D3" s="1">
         <v>632290</v>
       </c>
-      <c r="E3" s="1">
-        <v>632290</v>
+      <c r="E3">
+        <v>24</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -562,8 +570,8 @@
       <c r="D4" s="1">
         <v>629680</v>
       </c>
-      <c r="E4" s="1">
-        <v>629680</v>
+      <c r="E4">
+        <v>24</v>
       </c>
       <c r="F4">
         <v>13</v>
@@ -597,8 +605,8 @@
       <c r="D5" s="1">
         <v>625828</v>
       </c>
-      <c r="E5" s="1">
-        <v>625828</v>
+      <c r="E5">
+        <v>24</v>
       </c>
       <c r="F5">
         <v>13</v>
@@ -632,8 +640,8 @@
       <c r="D6" s="1">
         <v>616264</v>
       </c>
-      <c r="E6" s="1">
-        <v>616264</v>
+      <c r="E6">
+        <v>24</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -667,8 +675,8 @@
       <c r="D7" s="1">
         <v>702359</v>
       </c>
-      <c r="E7" s="1">
-        <v>702359</v>
+      <c r="E7">
+        <v>24</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -702,8 +710,8 @@
       <c r="D8" s="1">
         <v>707378</v>
       </c>
-      <c r="E8" s="1">
-        <v>707378</v>
+      <c r="E8">
+        <v>25</v>
       </c>
       <c r="F8">
         <v>14</v>
@@ -737,8 +745,8 @@
       <c r="D9" s="1">
         <v>706487</v>
       </c>
-      <c r="E9" s="1">
-        <v>706487</v>
+      <c r="E9">
+        <v>25</v>
       </c>
       <c r="F9">
         <v>14</v>
@@ -772,8 +780,8 @@
       <c r="D10" s="1">
         <v>707180</v>
       </c>
-      <c r="E10" s="1">
-        <v>707180</v>
+      <c r="E10">
+        <v>24</v>
       </c>
       <c r="F10">
         <v>14</v>
@@ -807,8 +815,8 @@
       <c r="D11" s="1">
         <v>704564</v>
       </c>
-      <c r="E11" s="1">
-        <v>704564</v>
+      <c r="E11">
+        <v>24</v>
       </c>
       <c r="F11">
         <v>14</v>
@@ -842,8 +850,8 @@
       <c r="D12" s="1">
         <v>704467</v>
       </c>
-      <c r="E12" s="1">
-        <v>704467</v>
+      <c r="E12">
+        <v>24</v>
       </c>
       <c r="F12">
         <v>14</v>
@@ -877,8 +885,8 @@
       <c r="D13" s="1">
         <v>704602</v>
       </c>
-      <c r="E13" s="1">
-        <v>704602</v>
+      <c r="E13">
+        <v>24</v>
       </c>
       <c r="F13">
         <v>14</v>
@@ -912,8 +920,8 @@
       <c r="D14" s="1">
         <v>704273</v>
       </c>
-      <c r="E14" s="1">
-        <v>704273</v>
+      <c r="E14">
+        <v>24</v>
       </c>
       <c r="F14">
         <v>14</v>
@@ -947,8 +955,8 @@
       <c r="D15" s="1">
         <v>709613</v>
       </c>
-      <c r="E15" s="1">
-        <v>709613</v>
+      <c r="E15">
+        <v>24</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -982,8 +990,8 @@
       <c r="D16" s="1">
         <v>709704</v>
       </c>
-      <c r="E16" s="1">
-        <v>709704</v>
+      <c r="E16">
+        <v>24</v>
       </c>
       <c r="F16">
         <v>14</v>
@@ -1017,8 +1025,8 @@
       <c r="D17" s="1">
         <v>703482</v>
       </c>
-      <c r="E17" s="1">
-        <v>703482</v>
+      <c r="E17">
+        <v>24</v>
       </c>
       <c r="F17">
         <v>14</v>
@@ -1052,8 +1060,8 @@
       <c r="D18" s="1">
         <v>707810</v>
       </c>
-      <c r="E18" s="1">
-        <v>707810</v>
+      <c r="E18">
+        <v>25</v>
       </c>
       <c r="F18">
         <v>15</v>
@@ -1087,8 +1095,8 @@
       <c r="D19" s="1">
         <v>703578</v>
       </c>
-      <c r="E19" s="1">
-        <v>703578</v>
+      <c r="E19">
+        <v>25</v>
       </c>
       <c r="F19">
         <v>15</v>
@@ -1122,8 +1130,8 @@
       <c r="D20" s="1">
         <v>701306</v>
       </c>
-      <c r="E20" s="1">
-        <v>701306</v>
+      <c r="E20">
+        <v>25</v>
       </c>
       <c r="F20">
         <v>15</v>
@@ -1157,8 +1165,8 @@
       <c r="D21" s="1">
         <v>700142</v>
       </c>
-      <c r="E21" s="1">
-        <v>700142</v>
+      <c r="E21">
+        <v>25</v>
       </c>
       <c r="F21">
         <v>15</v>
@@ -1192,8 +1200,8 @@
       <c r="D22" s="1">
         <v>687178</v>
       </c>
-      <c r="E22" s="1">
-        <v>687178</v>
+      <c r="E22">
+        <v>25</v>
       </c>
       <c r="F22">
         <v>15</v>
@@ -1227,8 +1235,8 @@
       <c r="D23" s="1">
         <v>703470</v>
       </c>
-      <c r="E23" s="1">
-        <v>703470</v>
+      <c r="E23">
+        <v>25</v>
       </c>
       <c r="F23">
         <v>15</v>
@@ -1262,8 +1270,8 @@
       <c r="D24" s="1">
         <v>702576</v>
       </c>
-      <c r="E24" s="1">
-        <v>702576</v>
+      <c r="E24">
+        <v>25</v>
       </c>
       <c r="F24">
         <v>15</v>
@@ -1297,8 +1305,8 @@
       <c r="D25" s="1">
         <v>707740</v>
       </c>
-      <c r="E25" s="1">
-        <v>707740</v>
+      <c r="E25">
+        <v>25</v>
       </c>
       <c r="F25">
         <v>15</v>
@@ -1332,8 +1340,8 @@
       <c r="D26" s="1">
         <v>746571</v>
       </c>
-      <c r="E26" s="1">
-        <v>746571</v>
+      <c r="E26">
+        <v>24</v>
       </c>
       <c r="F26">
         <v>14</v>
@@ -1367,8 +1375,8 @@
       <c r="D27" s="1">
         <v>747356</v>
       </c>
-      <c r="E27" s="1">
-        <v>747356</v>
+      <c r="E27">
+        <v>24</v>
       </c>
       <c r="F27">
         <v>14</v>
@@ -1402,8 +1410,8 @@
       <c r="D28" s="1">
         <v>749883</v>
       </c>
-      <c r="E28" s="1">
-        <v>749883</v>
+      <c r="E28">
+        <v>25</v>
       </c>
       <c r="F28">
         <v>15</v>
@@ -1437,8 +1445,8 @@
       <c r="D29" s="1">
         <v>750887</v>
       </c>
-      <c r="E29" s="1">
-        <v>750887</v>
+      <c r="E29">
+        <v>25</v>
       </c>
       <c r="F29">
         <v>16</v>
@@ -1472,8 +1480,8 @@
       <c r="D30" s="1">
         <v>752472</v>
       </c>
-      <c r="E30" s="1">
-        <v>752472</v>
+      <c r="E30">
+        <v>25</v>
       </c>
       <c r="F30">
         <v>16</v>
@@ -1507,8 +1515,8 @@
       <c r="D31" s="1">
         <v>753880</v>
       </c>
-      <c r="E31" s="1">
-        <v>753880</v>
+      <c r="E31">
+        <v>24</v>
       </c>
       <c r="F31">
         <v>16</v>
@@ -1542,8 +1550,8 @@
       <c r="D32" s="1">
         <v>842771</v>
       </c>
-      <c r="E32" s="1">
-        <v>842771</v>
+      <c r="E32">
+        <v>24</v>
       </c>
       <c r="F32">
         <v>16</v>
@@ -1577,8 +1585,8 @@
       <c r="D33" s="1">
         <v>839358</v>
       </c>
-      <c r="E33" s="1">
-        <v>839358</v>
+      <c r="E33">
+        <v>24</v>
       </c>
       <c r="F33">
         <v>16</v>
@@ -1612,8 +1620,8 @@
       <c r="D34" s="1">
         <v>826404</v>
       </c>
-      <c r="E34" s="1">
-        <v>826404</v>
+      <c r="E34">
+        <v>24</v>
       </c>
       <c r="F34">
         <v>16</v>
@@ -1647,8 +1655,8 @@
       <c r="D35" s="1">
         <v>825788</v>
       </c>
-      <c r="E35" s="1">
-        <v>825788</v>
+      <c r="E35">
+        <v>25</v>
       </c>
       <c r="F35">
         <v>16</v>
@@ -1682,8 +1690,8 @@
       <c r="D36" s="1">
         <v>826144</v>
       </c>
-      <c r="E36" s="1">
-        <v>826144</v>
+      <c r="E36">
+        <v>25</v>
       </c>
       <c r="F36">
         <v>16</v>
@@ -1717,8 +1725,8 @@
       <c r="D37" s="1">
         <v>824528</v>
       </c>
-      <c r="E37" s="1">
-        <v>824528</v>
+      <c r="E37">
+        <v>25</v>
       </c>
       <c r="F37">
         <v>16</v>
@@ -1752,8 +1760,8 @@
       <c r="D38" s="1">
         <v>848264</v>
       </c>
-      <c r="E38" s="1">
-        <v>848264</v>
+      <c r="E38">
+        <v>25</v>
       </c>
       <c r="F38">
         <v>16</v>
@@ -1787,8 +1795,8 @@
       <c r="D39" s="1">
         <v>857783</v>
       </c>
-      <c r="E39" s="1">
-        <v>857783</v>
+      <c r="E39">
+        <v>24</v>
       </c>
       <c r="F39">
         <v>16</v>
@@ -1822,8 +1830,8 @@
       <c r="D40" s="1">
         <v>857368</v>
       </c>
-      <c r="E40" s="1">
-        <v>857368</v>
+      <c r="E40">
+        <v>24</v>
       </c>
       <c r="F40">
         <v>16</v>
@@ -1857,8 +1865,8 @@
       <c r="D41" s="1">
         <v>857057</v>
       </c>
-      <c r="E41" s="1">
-        <v>857057</v>
+      <c r="E41">
+        <v>25</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1892,8 +1900,8 @@
       <c r="D42" s="1">
         <v>855300</v>
       </c>
-      <c r="E42" s="1">
-        <v>855300</v>
+      <c r="E42">
+        <v>25</v>
       </c>
       <c r="F42">
         <v>17</v>
@@ -1927,8 +1935,8 @@
       <c r="D43" s="1">
         <v>853372</v>
       </c>
-      <c r="E43" s="1">
-        <v>853372</v>
+      <c r="E43">
+        <v>25</v>
       </c>
       <c r="F43">
         <v>17</v>
@@ -1962,8 +1970,8 @@
       <c r="D44" s="1">
         <v>833000</v>
       </c>
-      <c r="E44" s="1">
-        <v>833000</v>
+      <c r="E44">
+        <v>27</v>
       </c>
       <c r="F44">
         <v>18</v>
@@ -1997,8 +2005,8 @@
       <c r="D45" s="1">
         <v>837272</v>
       </c>
-      <c r="E45" s="1">
-        <v>837272</v>
+      <c r="E45">
+        <v>27</v>
       </c>
       <c r="F45">
         <v>17</v>
@@ -2032,8 +2040,8 @@
       <c r="D46" s="1">
         <v>826641</v>
       </c>
-      <c r="E46" s="1">
-        <v>826641</v>
+      <c r="E46">
+        <v>28</v>
       </c>
       <c r="F46">
         <v>18</v>
@@ -2067,8 +2075,8 @@
       <c r="D47" s="1">
         <v>825854</v>
       </c>
-      <c r="E47" s="1">
-        <v>825854</v>
+      <c r="E47">
+        <v>27</v>
       </c>
       <c r="F47">
         <v>18</v>
@@ -2102,8 +2110,8 @@
       <c r="D48" s="1">
         <v>822853</v>
       </c>
-      <c r="E48" s="1">
-        <v>822853</v>
+      <c r="E48">
+        <v>28</v>
       </c>
       <c r="F48">
         <v>19</v>
@@ -2137,8 +2145,8 @@
       <c r="D49" s="1">
         <v>819190</v>
       </c>
-      <c r="E49" s="1">
-        <v>819190</v>
+      <c r="E49">
+        <v>30</v>
       </c>
       <c r="F49">
         <v>20</v>
@@ -2172,8 +2180,8 @@
       <c r="D50" s="1">
         <v>825469</v>
       </c>
-      <c r="E50" s="1">
-        <v>825469</v>
+      <c r="E50">
+        <v>31</v>
       </c>
       <c r="F50">
         <v>21</v>
@@ -2207,8 +2215,8 @@
       <c r="D51" s="1">
         <v>823204</v>
       </c>
-      <c r="E51" s="1">
-        <v>823204</v>
+      <c r="E51">
+        <v>30</v>
       </c>
       <c r="F51">
         <v>21</v>
@@ -2242,8 +2250,8 @@
       <c r="D52" s="1">
         <v>823524</v>
       </c>
-      <c r="E52" s="1">
-        <v>823524</v>
+      <c r="E52">
+        <v>28</v>
       </c>
       <c r="F52">
         <v>19</v>
@@ -2277,8 +2285,8 @@
       <c r="D53" s="1">
         <v>821321</v>
       </c>
-      <c r="E53" s="1">
-        <v>821321</v>
+      <c r="E53">
+        <v>29</v>
       </c>
       <c r="F53">
         <v>20</v>
@@ -2312,8 +2320,8 @@
       <c r="D54" s="1">
         <v>818724</v>
       </c>
-      <c r="E54" s="1">
-        <v>818724</v>
+      <c r="E54">
+        <v>29</v>
       </c>
       <c r="F54">
         <v>21</v>
@@ -2347,8 +2355,8 @@
       <c r="D55" s="1">
         <v>816212</v>
       </c>
-      <c r="E55" s="1">
-        <v>816212</v>
+      <c r="E55">
+        <v>29</v>
       </c>
       <c r="F55">
         <v>21</v>
@@ -2382,8 +2390,8 @@
       <c r="D56" s="1">
         <v>859009</v>
       </c>
-      <c r="E56" s="1">
-        <v>859009</v>
+      <c r="E56">
+        <v>29</v>
       </c>
       <c r="F56">
         <v>21</v>
@@ -2417,8 +2425,8 @@
       <c r="D57" s="1">
         <v>860986</v>
       </c>
-      <c r="E57" s="1">
-        <v>860986</v>
+      <c r="E57">
+        <v>30</v>
       </c>
       <c r="F57">
         <v>22</v>
@@ -2452,8 +2460,8 @@
       <c r="D58" s="1">
         <v>853614</v>
       </c>
-      <c r="E58" s="1">
-        <v>853614</v>
+      <c r="E58">
+        <v>32</v>
       </c>
       <c r="F58">
         <v>23</v>
@@ -2487,8 +2495,8 @@
       <c r="D59" s="1">
         <v>860634</v>
       </c>
-      <c r="E59" s="1">
-        <v>860634</v>
+      <c r="E59">
+        <v>34</v>
       </c>
       <c r="F59">
         <v>25</v>
@@ -2522,8 +2530,8 @@
       <c r="D60" s="1">
         <v>862059</v>
       </c>
-      <c r="E60" s="1">
-        <v>862059</v>
+      <c r="E60">
+        <v>35</v>
       </c>
       <c r="F60">
         <v>26</v>
@@ -2557,8 +2565,8 @@
       <c r="D61" s="1">
         <v>862864</v>
       </c>
-      <c r="E61" s="1">
-        <v>862864</v>
+      <c r="E61">
+        <v>37</v>
       </c>
       <c r="F61">
         <v>28</v>
@@ -2592,8 +2600,8 @@
       <c r="D62" s="1">
         <v>859140</v>
       </c>
-      <c r="E62" s="1">
-        <v>859140</v>
+      <c r="E62">
+        <v>34</v>
       </c>
       <c r="F62">
         <v>26</v>
@@ -2627,8 +2635,8 @@
       <c r="D63" s="1">
         <v>860841</v>
       </c>
-      <c r="E63" s="1">
-        <v>860841</v>
+      <c r="E63">
+        <v>37</v>
       </c>
       <c r="F63">
         <v>28</v>
@@ -2662,8 +2670,8 @@
       <c r="D64" s="1">
         <v>866032</v>
       </c>
-      <c r="E64" s="1">
-        <v>866032</v>
+      <c r="E64">
+        <v>37</v>
       </c>
       <c r="F64">
         <v>28</v>
@@ -2697,8 +2705,8 @@
       <c r="D65" s="1">
         <v>866132</v>
       </c>
-      <c r="E65" s="1">
-        <v>866132</v>
+      <c r="E65">
+        <v>37</v>
       </c>
       <c r="F65">
         <v>28</v>
@@ -2732,8 +2740,8 @@
       <c r="D66" s="1">
         <v>870590</v>
       </c>
-      <c r="E66" s="1">
-        <v>870590</v>
+      <c r="E66">
+        <v>37</v>
       </c>
       <c r="F66">
         <v>28</v>
@@ -2767,8 +2775,8 @@
       <c r="D67" s="1">
         <v>853642</v>
       </c>
-      <c r="E67" s="1">
-        <v>853642</v>
+      <c r="E67">
+        <v>37</v>
       </c>
       <c r="F67">
         <v>28</v>
@@ -2802,8 +2810,8 @@
       <c r="D68" s="1">
         <v>856553</v>
       </c>
-      <c r="E68" s="1">
-        <v>856553</v>
+      <c r="E68">
+        <v>35</v>
       </c>
       <c r="F68">
         <v>26</v>
@@ -2837,8 +2845,8 @@
       <c r="D69" s="1">
         <v>856586</v>
       </c>
-      <c r="E69" s="1">
-        <v>856586</v>
+      <c r="E69">
+        <v>35</v>
       </c>
       <c r="F69">
         <v>26</v>
@@ -2872,8 +2880,8 @@
       <c r="D70" s="1">
         <v>845192</v>
       </c>
-      <c r="E70" s="1">
-        <v>845192</v>
+      <c r="E70">
+        <v>37</v>
       </c>
       <c r="F70">
         <v>28</v>
@@ -2907,8 +2915,8 @@
       <c r="D71" s="1">
         <v>853003</v>
       </c>
-      <c r="E71" s="1">
-        <v>853003</v>
+      <c r="E71">
+        <v>38</v>
       </c>
       <c r="F71">
         <v>29</v>
@@ -2942,8 +2950,8 @@
       <c r="D72" s="1">
         <v>852171</v>
       </c>
-      <c r="E72" s="1">
-        <v>852171</v>
+      <c r="E72">
+        <v>35</v>
       </c>
       <c r="F72">
         <v>27</v>
@@ -2977,8 +2985,8 @@
       <c r="D73" s="1">
         <v>854853</v>
       </c>
-      <c r="E73" s="1">
-        <v>854853</v>
+      <c r="E73">
+        <v>35</v>
       </c>
       <c r="F73">
         <v>28</v>
@@ -3012,8 +3020,8 @@
       <c r="D74" s="1">
         <v>858146</v>
       </c>
-      <c r="E74" s="1">
-        <v>858146</v>
+      <c r="E74">
+        <v>35</v>
       </c>
       <c r="F74">
         <v>28</v>
@@ -3047,8 +3055,8 @@
       <c r="D75" s="1">
         <v>866740</v>
       </c>
-      <c r="E75" s="1">
-        <v>866740</v>
+      <c r="E75">
+        <v>36</v>
       </c>
       <c r="F75">
         <v>29</v>
@@ -3082,8 +3090,8 @@
       <c r="D76" s="1">
         <v>869817</v>
       </c>
-      <c r="E76" s="1">
-        <v>869817</v>
+      <c r="E76">
+        <v>37</v>
       </c>
       <c r="F76">
         <v>30</v>
@@ -3117,8 +3125,8 @@
       <c r="D77" s="1">
         <v>10765</v>
       </c>
-      <c r="E77" s="1">
-        <v>10765</v>
+      <c r="E77">
+        <v>37</v>
       </c>
       <c r="F77">
         <v>30</v>
@@ -3152,8 +3160,8 @@
       <c r="D78" s="1">
         <v>6596</v>
       </c>
-      <c r="E78" s="1">
-        <v>6596</v>
+      <c r="E78">
+        <v>37</v>
       </c>
       <c r="F78">
         <v>30</v>
@@ -3187,8 +3195,8 @@
       <c r="D79" s="1">
         <v>6067</v>
       </c>
-      <c r="E79" s="1">
-        <v>6067</v>
+      <c r="E79">
+        <v>39</v>
       </c>
       <c r="F79">
         <v>32</v>
@@ -3222,8 +3230,8 @@
       <c r="D80" s="1">
         <v>7869</v>
       </c>
-      <c r="E80" s="1">
-        <v>7869</v>
+      <c r="E80">
+        <v>39</v>
       </c>
       <c r="F80">
         <v>31</v>
@@ -3257,8 +3265,8 @@
       <c r="D81" s="1">
         <v>7870</v>
       </c>
-      <c r="E81" s="1">
-        <v>7870</v>
+      <c r="E81">
+        <v>40</v>
       </c>
       <c r="F81">
         <v>32</v>
@@ -3292,8 +3300,8 @@
       <c r="D82" s="1">
         <v>285746</v>
       </c>
-      <c r="E82" s="1">
-        <v>285746</v>
+      <c r="E82">
+        <v>39</v>
       </c>
       <c r="F82">
         <v>32</v>
@@ -3327,8 +3335,8 @@
       <c r="D83" s="1">
         <v>291224</v>
       </c>
-      <c r="E83" s="1">
-        <v>291224</v>
+      <c r="E83">
+        <v>40</v>
       </c>
       <c r="F83">
         <v>32</v>
@@ -3362,8 +3370,8 @@
       <c r="D84" s="1">
         <v>294230</v>
       </c>
-      <c r="E84" s="1">
-        <v>294230</v>
+      <c r="E84">
+        <v>39</v>
       </c>
       <c r="F84">
         <v>32</v>
@@ -3397,8 +3405,8 @@
       <c r="D85" s="1">
         <v>302299</v>
       </c>
-      <c r="E85" s="1">
-        <v>302299</v>
+      <c r="E85">
+        <v>38</v>
       </c>
       <c r="F85">
         <v>31</v>
@@ -3432,8 +3440,8 @@
       <c r="D86" s="1">
         <v>877743</v>
       </c>
-      <c r="E86" s="1">
-        <v>877743</v>
+      <c r="E86">
+        <v>38</v>
       </c>
       <c r="F86">
         <v>31</v>
@@ -3467,8 +3475,8 @@
       <c r="D87" s="1">
         <v>867716</v>
       </c>
-      <c r="E87" s="1">
-        <v>867716</v>
+      <c r="E87">
+        <v>37</v>
       </c>
       <c r="F87">
         <v>31</v>
@@ -3502,8 +3510,8 @@
       <c r="D88" s="1">
         <v>867556</v>
       </c>
-      <c r="E88" s="1">
-        <v>867556</v>
+      <c r="E88">
+        <v>37</v>
       </c>
       <c r="F88">
         <v>31</v>
@@ -3537,8 +3545,8 @@
       <c r="D89" s="1">
         <v>675114</v>
       </c>
-      <c r="E89" s="1">
-        <v>675114</v>
+      <c r="E89">
+        <v>35</v>
       </c>
       <c r="F89">
         <v>29</v>
@@ -3572,8 +3580,8 @@
       <c r="D90" s="1">
         <v>677850</v>
       </c>
-      <c r="E90" s="1">
-        <v>677850</v>
+      <c r="E90">
+        <v>36</v>
       </c>
       <c r="F90">
         <v>29</v>
@@ -3607,8 +3615,8 @@
       <c r="D91" s="1">
         <v>679432</v>
       </c>
-      <c r="E91" s="1">
-        <v>679432</v>
+      <c r="E91">
+        <v>36</v>
       </c>
       <c r="F91">
         <v>30</v>
@@ -3642,8 +3650,8 @@
       <c r="D92" s="1">
         <v>680460</v>
       </c>
-      <c r="E92" s="1">
-        <v>680460</v>
+      <c r="E92">
+        <v>37</v>
       </c>
       <c r="F92">
         <v>31</v>
@@ -3677,8 +3685,8 @@
       <c r="D93" s="1">
         <v>682098</v>
       </c>
-      <c r="E93" s="1">
-        <v>682098</v>
+      <c r="E93">
+        <v>37</v>
       </c>
       <c r="F93">
         <v>31</v>
@@ -3712,8 +3720,8 @@
       <c r="D94" s="1">
         <v>683666</v>
       </c>
-      <c r="E94" s="1">
-        <v>683666</v>
+      <c r="E94">
+        <v>37</v>
       </c>
       <c r="F94">
         <v>31</v>
@@ -3747,8 +3755,8 @@
       <c r="D95" s="1">
         <v>684012</v>
       </c>
-      <c r="E95" s="1">
-        <v>684012</v>
+      <c r="E95">
+        <v>37</v>
       </c>
       <c r="F95">
         <v>31</v>
@@ -3783,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F96">
         <v>31</v>
@@ -3818,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F97">
         <v>32</v>
@@ -3853,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F98">
         <v>32</v>
@@ -3888,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F99">
         <v>31</v>
@@ -3923,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F100">
         <v>32</v>
@@ -3958,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F101">
         <v>32</v>
@@ -3993,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -4028,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F103">
         <v>39</v>
@@ -4063,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F104">
         <v>40</v>
@@ -4098,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F105">
         <v>39</v>
@@ -4133,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F106">
         <v>43</v>
@@ -4168,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F107">
         <v>46</v>
@@ -4203,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F108">
         <v>46</v>
@@ -4238,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F109">
         <v>48</v>
@@ -4273,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F110">
         <v>49</v>
@@ -4308,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F111">
         <v>49</v>
@@ -4342,8 +4350,8 @@
       <c r="D112" s="1">
         <v>2814157</v>
       </c>
-      <c r="E112" s="1">
-        <v>2814157</v>
+      <c r="E112">
+        <v>57</v>
       </c>
       <c r="F112">
         <v>50</v>
@@ -4377,8 +4385,8 @@
       <c r="D113" s="1">
         <v>2802884</v>
       </c>
-      <c r="E113" s="1">
-        <v>2802884</v>
+      <c r="E113">
+        <v>59</v>
       </c>
       <c r="F113">
         <v>52</v>
@@ -4412,8 +4420,8 @@
       <c r="D114" s="1">
         <v>2827158</v>
       </c>
-      <c r="E114" s="1">
-        <v>2827158</v>
+      <c r="E114">
+        <v>59</v>
       </c>
       <c r="F114">
         <v>52</v>
@@ -4447,8 +4455,8 @@
       <c r="D115" s="1">
         <v>3293235</v>
       </c>
-      <c r="E115" s="1">
-        <v>3293235</v>
+      <c r="E115">
+        <v>61</v>
       </c>
       <c r="F115">
         <v>54</v>
@@ -4482,8 +4490,8 @@
       <c r="D116" s="1">
         <v>3046351</v>
       </c>
-      <c r="E116" s="1">
-        <v>3046351</v>
+      <c r="E116">
+        <v>63</v>
       </c>
       <c r="F116">
         <v>56</v>
@@ -4517,8 +4525,8 @@
       <c r="D117" s="1">
         <v>3048990</v>
       </c>
-      <c r="E117" s="1">
-        <v>3048990</v>
+      <c r="E117">
+        <v>65</v>
       </c>
       <c r="F117">
         <v>58</v>
@@ -4552,8 +4560,8 @@
       <c r="D118" s="1">
         <v>3075026</v>
       </c>
-      <c r="E118" s="1">
-        <v>3075026</v>
+      <c r="E118">
+        <v>63</v>
       </c>
       <c r="F118">
         <v>56</v>
@@ -4587,8 +4595,8 @@
       <c r="D119" s="1">
         <v>3273093</v>
       </c>
-      <c r="E119" s="1">
-        <v>3273093</v>
+      <c r="E119">
+        <v>63</v>
       </c>
       <c r="F119">
         <v>56</v>
@@ -4622,8 +4630,8 @@
       <c r="D120" s="1">
         <v>3146631</v>
       </c>
-      <c r="E120" s="1">
-        <v>3146631</v>
+      <c r="E120">
+        <v>65</v>
       </c>
       <c r="F120">
         <v>58</v>
@@ -4657,8 +4665,8 @@
       <c r="D121" s="1">
         <v>3116757</v>
       </c>
-      <c r="E121" s="1">
-        <v>3116757</v>
+      <c r="E121">
+        <v>63</v>
       </c>
       <c r="F121">
         <v>57</v>
@@ -4692,8 +4700,8 @@
       <c r="D122" s="1">
         <v>3180405</v>
       </c>
-      <c r="E122" s="1">
-        <v>3180405</v>
+      <c r="E122">
+        <v>64</v>
       </c>
       <c r="F122">
         <v>58</v>
@@ -4727,8 +4735,8 @@
       <c r="D123" s="1">
         <v>3175183</v>
       </c>
-      <c r="E123" s="1">
-        <v>3175183</v>
+      <c r="E123">
+        <v>64</v>
       </c>
       <c r="F123">
         <v>58</v>
@@ -4762,8 +4770,8 @@
       <c r="D124" s="1">
         <v>3098802</v>
       </c>
-      <c r="E124" s="1">
-        <v>3098802</v>
+      <c r="E124">
+        <v>65</v>
       </c>
       <c r="F124">
         <v>59</v>
@@ -4797,8 +4805,8 @@
       <c r="D125" s="1">
         <v>3096500</v>
       </c>
-      <c r="E125" s="1">
-        <v>3096500</v>
+      <c r="E125">
+        <v>66</v>
       </c>
       <c r="F125">
         <v>60</v>
@@ -4832,8 +4840,8 @@
       <c r="D126" s="1">
         <v>3092952</v>
       </c>
-      <c r="E126" s="1">
-        <v>3092952</v>
+      <c r="E126">
+        <v>65</v>
       </c>
       <c r="F126">
         <v>59</v>
@@ -4867,8 +4875,8 @@
       <c r="D127" s="1">
         <v>3091948</v>
       </c>
-      <c r="E127" s="1">
-        <v>3091948</v>
+      <c r="E127">
+        <v>66</v>
       </c>
       <c r="F127">
         <v>60</v>
@@ -4902,8 +4910,8 @@
       <c r="D128" s="1">
         <v>3117517</v>
       </c>
-      <c r="E128" s="1">
-        <v>3117517</v>
+      <c r="E128">
+        <v>66</v>
       </c>
       <c r="F128">
         <v>60</v>
@@ -4937,8 +4945,8 @@
       <c r="D129" s="1">
         <v>3095668</v>
       </c>
-      <c r="E129" s="1">
-        <v>3095668</v>
+      <c r="E129">
+        <v>68</v>
       </c>
       <c r="F129">
         <v>62</v>
@@ -4972,8 +4980,8 @@
       <c r="D130" s="1">
         <v>3085136</v>
       </c>
-      <c r="E130" s="1">
-        <v>3085136</v>
+      <c r="E130">
+        <v>70</v>
       </c>
       <c r="F130">
         <v>64</v>
@@ -5007,8 +5015,8 @@
       <c r="D131" s="1">
         <v>3067495</v>
       </c>
-      <c r="E131" s="1">
-        <v>3067495</v>
+      <c r="E131">
+        <v>71</v>
       </c>
       <c r="F131">
         <v>65</v>
@@ -5042,8 +5050,8 @@
       <c r="D132" s="1">
         <v>3064061</v>
       </c>
-      <c r="E132" s="1">
-        <v>3064061</v>
+      <c r="E132">
+        <v>71</v>
       </c>
       <c r="F132">
         <v>65</v>
@@ -5077,8 +5085,8 @@
       <c r="D133" s="1">
         <v>3074207</v>
       </c>
-      <c r="E133" s="1">
-        <v>3074207</v>
+      <c r="E133">
+        <v>70</v>
       </c>
       <c r="F133">
         <v>65</v>
@@ -5112,8 +5120,8 @@
       <c r="D134" s="1">
         <v>2999855</v>
       </c>
-      <c r="E134" s="1">
-        <v>2999855</v>
+      <c r="E134">
+        <v>71</v>
       </c>
       <c r="F134">
         <v>66</v>
@@ -5147,8 +5155,8 @@
       <c r="D135" s="1">
         <v>2960419</v>
       </c>
-      <c r="E135" s="1">
-        <v>2960419</v>
+      <c r="E135">
+        <v>70</v>
       </c>
       <c r="F135">
         <v>66</v>
@@ -5182,8 +5190,8 @@
       <c r="D136" s="1">
         <v>2984431</v>
       </c>
-      <c r="E136" s="1">
-        <v>2984431</v>
+      <c r="E136">
+        <v>70</v>
       </c>
       <c r="F136">
         <v>66</v>
@@ -5217,8 +5225,8 @@
       <c r="D137" s="1">
         <v>2982780</v>
       </c>
-      <c r="E137" s="1">
-        <v>2982780</v>
+      <c r="E137">
+        <v>72</v>
       </c>
       <c r="F137">
         <v>68</v>
@@ -5252,8 +5260,8 @@
       <c r="D138" s="1">
         <v>2977355</v>
       </c>
-      <c r="E138" s="1">
-        <v>2977355</v>
+      <c r="E138">
+        <v>75</v>
       </c>
       <c r="F138">
         <v>71</v>
@@ -5287,8 +5295,8 @@
       <c r="D139" s="1">
         <v>3008049</v>
       </c>
-      <c r="E139" s="1">
-        <v>3008049</v>
+      <c r="E139">
+        <v>75</v>
       </c>
       <c r="F139">
         <v>71</v>
@@ -5322,8 +5330,8 @@
       <c r="D140" s="1">
         <v>2958454</v>
       </c>
-      <c r="E140" s="1">
-        <v>2958454</v>
+      <c r="E140">
+        <v>77</v>
       </c>
       <c r="F140">
         <v>73</v>
@@ -5357,8 +5365,8 @@
       <c r="D141" s="1">
         <v>2866523</v>
       </c>
-      <c r="E141" s="1">
-        <v>2866523</v>
+      <c r="E141">
+        <v>78</v>
       </c>
       <c r="F141">
         <v>74</v>
@@ -5392,8 +5400,8 @@
       <c r="D142" s="1">
         <v>2871219</v>
       </c>
-      <c r="E142" s="1">
-        <v>2871219</v>
+      <c r="E142">
+        <v>83</v>
       </c>
       <c r="F142">
         <v>79</v>
@@ -5427,8 +5435,8 @@
       <c r="D143" s="1">
         <v>2861710</v>
       </c>
-      <c r="E143" s="1">
-        <v>2861710</v>
+      <c r="E143">
+        <v>89</v>
       </c>
       <c r="F143">
         <v>85</v>
@@ -5462,8 +5470,8 @@
       <c r="D144" s="1">
         <v>2849237</v>
       </c>
-      <c r="E144" s="1">
-        <v>2849237</v>
+      <c r="E144">
+        <v>89</v>
       </c>
       <c r="F144">
         <v>84</v>
@@ -5497,8 +5505,8 @@
       <c r="D145" s="1">
         <v>2896603</v>
       </c>
-      <c r="E145" s="1">
-        <v>2896603</v>
+      <c r="E145">
+        <v>91</v>
       </c>
       <c r="F145">
         <v>86</v>
@@ -5532,8 +5540,8 @@
       <c r="D146" s="1">
         <v>2896577</v>
       </c>
-      <c r="E146" s="1">
-        <v>2896577</v>
+      <c r="E146">
+        <v>95</v>
       </c>
       <c r="F146">
         <v>90</v>
@@ -5567,8 +5575,8 @@
       <c r="D147" s="1">
         <v>2828177</v>
       </c>
-      <c r="E147" s="1">
-        <v>2828177</v>
+      <c r="E147">
+        <v>100</v>
       </c>
       <c r="F147">
         <v>94</v>
@@ -5602,8 +5610,8 @@
       <c r="D148" s="1">
         <v>2834501</v>
       </c>
-      <c r="E148" s="1">
-        <v>2834501</v>
+      <c r="E148">
+        <v>102</v>
       </c>
       <c r="F148">
         <v>96</v>
@@ -5637,8 +5645,8 @@
       <c r="D149" s="1">
         <v>2798167</v>
       </c>
-      <c r="E149" s="1">
-        <v>2798167</v>
+      <c r="E149">
+        <v>0</v>
       </c>
       <c r="F149">
         <v>0</v>
